--- a/src/pyuniclass/data/Uniclass2015_EF_v1_15.xlsx
+++ b/src/pyuniclass/data/Uniclass2015_EF_v1_15.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BrookA\source\repos\NBS.Uniclass.Publishing\src\NBS.Uniclass.Publishing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KharinA\Dev\repos\nbs-uniclass-infrastructure\s3-contents\downloads\uniclass-all-2025-07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8898CAEE-C96D-45B8-9506-9753E5D9BA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15600BE6-3884-484A-AAED-CC5849FF0671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EF" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621" fullCalcOnLoad="1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="790">
-  <si>
-    <t>EF Elements/ functions - April 2024 - v1.15</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="790">
+  <si>
+    <t>EF Elements/ functions - July 2025 - v1.15</t>
   </si>
   <si>
     <t>Code</t>
@@ -2396,8 +2396,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2444,6 +2443,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2481,22 +2487,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyProtection="1"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2505,6 +2510,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="19">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2523,17 +2539,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2764,8 +2769,8 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="NRM1" dataDxfId="3"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="IFC 2x3 TC1" dataDxfId="2"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="IFC 4Add2 TC1"/>
-    <tableColumn id="14" xr3:uid="{7E231B53-0F11-45EB-B058-B4DD7CE438CD}" name="IFC 4x3Add2 TC1" dataDxfId="0"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="CESMM" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{7E231B53-0F11-45EB-B058-B4DD7CE438CD}" name="IFC 4x3Add2 TC1" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="CESMM" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="NBS" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3061,4957 +3066,4958 @@
   <dimension ref="A1:N233"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1" style="3"/>
-    <col min="2" max="6" width="12" customWidth="1" style="3"/>
-    <col min="7" max="7" width="71.42578125" customWidth="1" style="3"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1" style="3"/>
-    <col min="9" max="9" width="19" customWidth="1" style="3"/>
-    <col min="10" max="12" width="12" customWidth="1" style="3"/>
-    <col min="13" max="13" width="12.7109375" customWidth="1" style="3"/>
-    <col min="14" max="14" width="13" customWidth="1" style="3"/>
-    <col min="15" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
+    <col min="2" max="6" width="12" style="2" customWidth="1"/>
+    <col min="7" max="7" width="71.42578125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19" style="2" customWidth="1"/>
+    <col min="10" max="12" width="12" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="13" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="39.75" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:14" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-    </row>
-    <row r="2" ht="3" customHeight="1"/>
-    <row r="3" ht="37.5" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="3" customHeight="1" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="3" t="s">
+      <c r="H5" s="3"/>
+      <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="M9" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="M11" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="M12" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="L13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="M13" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="L14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="M14" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="I19" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="2" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="G22" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="I22" s="2" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="s">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="I23" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="s">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="D24" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="I24" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="L24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="M24" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="s">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="I25" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G26" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="I26" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="I27" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="L27" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="M27" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="s">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="D28" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="I28" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="L28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="M28" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="s">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G29" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="s">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="s">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="D31" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="I31" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="L31" s="3" t="s">
+      <c r="L31" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="M31" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="s">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="I32" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L32" s="3" t="s">
+      <c r="L32" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="M32" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="s">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="I33" s="3" t="s">
+      <c r="I33" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="L33" s="3" t="s">
+      <c r="L33" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M33" s="3" t="s">
+      <c r="M33" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="L34" s="3" t="s">
+      <c r="L34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="M34" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="L35" s="3" t="s">
+      <c r="L35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="M35" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="L36" s="3" t="s">
+      <c r="L36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="M36" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D38" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="L38" s="3" t="s">
+      <c r="L38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="M38" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="D39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="L39" s="3" t="s">
+      <c r="L39" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="M39" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G40" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="L40" s="3" t="s">
+      <c r="L40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="M40" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="D43" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="L43" s="3" t="s">
+      <c r="L43" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M43" s="3" t="s">
+      <c r="M43" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="L44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="M44" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G45" s="3" t="s">
+      <c r="G45" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="L45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="M45" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="D46" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="G46" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="I46" s="3" t="s">
+      <c r="I46" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L46" s="3" t="s">
+      <c r="L46" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M46" s="3" t="s">
+      <c r="M46" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="s">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="I47" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="s">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D48" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I48" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="L48" s="3" t="s">
+      <c r="L48" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="M48" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="s">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D49" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="2" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="s">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="D50" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="G50" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="I50" s="3" t="s">
+      <c r="I50" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="L50" s="3" t="s">
+      <c r="L50" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M50" s="3" t="s">
+      <c r="M50" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="s">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="D51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="I51" s="3" t="s">
+      <c r="I51" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="L51" s="3" t="s">
+      <c r="L51" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M51" s="3" t="s">
+      <c r="M51" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="s">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="L52" s="3" t="s">
+      <c r="L52" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="M52" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="s">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I53" s="3" t="s">
+      <c r="I53" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="s">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="D54" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I54" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="3" t="s">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="D55" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="I55" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="3" t="s">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="D56" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" s="2" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="s">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D57" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="I57" s="3" t="s">
+      <c r="I57" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="I58" s="3" t="s">
+      <c r="I58" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="s">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="D59" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I59" s="3" t="s">
+      <c r="I59" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="L59" s="3" t="s">
+      <c r="L59" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="M59" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="s">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D60" s="3" t="s">
+      <c r="D60" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="I60" s="3" t="s">
+      <c r="I60" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="L60" s="3" t="s">
+      <c r="L60" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="M60" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="s">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="I61" s="3" t="s">
+      <c r="I61" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="s">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="I62" s="3" t="s">
+      <c r="I62" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="3" t="s">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="I63" s="3" t="s">
+      <c r="I63" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="L63" s="3" t="s">
+      <c r="L63" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M63" s="3" t="s">
+      <c r="M63" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="3" t="s">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C64" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="I64" s="3" t="s">
+      <c r="I64" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="L64" s="3" t="s">
+      <c r="L64" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M64" s="3" t="s">
+      <c r="M64" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="3" t="s">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="I65" s="3" t="s">
+      <c r="I65" s="2" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="3" t="s">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C66" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="G66" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I66" s="3" t="s">
+      <c r="I66" s="2" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="s">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C67" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="I67" s="3" t="s">
+      <c r="I67" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="L67" s="3" t="s">
+      <c r="L67" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M67" s="3" t="s">
+      <c r="M67" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="3" t="s">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C68" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="I68" s="3" t="s">
+      <c r="I68" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="L68" s="3" t="s">
+      <c r="L68" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M68" s="3" t="s">
+      <c r="M68" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="3" t="s">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C69" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="I69" s="3" t="s">
+      <c r="I69" s="2" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="s">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I70" s="3" t="s">
+      <c r="I70" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="L70" s="3" t="s">
+      <c r="L70" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M70" s="3" t="s">
+      <c r="M70" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="3" t="s">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C71" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="I71" s="3" t="s">
+      <c r="I71" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="L71" s="3" t="s">
+      <c r="L71" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M71" s="3" t="s">
+      <c r="M71" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="3" t="s">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="I72" s="3" t="s">
+      <c r="I72" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="3" t="s">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C73" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="I73" s="3" t="s">
+      <c r="I73" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C74" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G74" s="3" t="s">
+      <c r="G74" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="I74" s="3" t="s">
+      <c r="I74" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="L74" s="3" t="s">
+      <c r="L74" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M74" s="3" t="s">
+      <c r="M74" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="3" t="s">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C75" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I75" s="3" t="s">
+      <c r="I75" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="L75" s="3" t="s">
+      <c r="L75" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="M75" s="3" t="s">
+      <c r="M75" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="s">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C76" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I76" s="3" t="s">
+      <c r="I76" s="2" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="3" t="s">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="C77" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="I77" s="3" t="s">
+      <c r="I77" s="2" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="3" t="s">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="C78" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="I78" s="3" t="s">
+      <c r="I78" s="2" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="s">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="C79" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="I79" s="3" t="s">
+      <c r="I79" s="2" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="3" t="s">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="C80" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="I80" s="3" t="s">
+      <c r="I80" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="3" t="s">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C81" s="3" t="s">
+      <c r="C81" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="2" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="s">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C82" s="3" t="s">
+      <c r="C82" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="I82" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="3" t="s">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="C83" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="G83" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="I83" s="2" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="C84" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="I84" s="3" t="s">
+      <c r="I84" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="3" t="s">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="C85" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="I85" s="3" t="s">
+      <c r="I85" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="3" t="s">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G86" s="3" t="s">
+      <c r="G86" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="I86" s="3" t="s">
+      <c r="I86" s="2" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="3" t="s">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="C87" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G87" s="3" t="s">
+      <c r="G87" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I87" s="3" t="s">
+      <c r="I87" s="2" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="3" t="s">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="C88" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G88" s="3" t="s">
+      <c r="G88" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="I88" s="3" t="s">
+      <c r="I88" s="2" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="3" t="s">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="C89" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G89" s="3" t="s">
+      <c r="G89" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="I89" s="3" t="s">
+      <c r="I89" s="2" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="3" t="s">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C90" s="3" t="s">
+      <c r="C90" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G90" s="3" t="s">
+      <c r="G90" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="I90" s="3" t="s">
+      <c r="I90" s="2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="3" t="s">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C91" s="3" t="s">
+      <c r="C91" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="I91" s="3" t="s">
+      <c r="I91" s="2" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="3" t="s">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C92" s="3" t="s">
+      <c r="C92" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="I92" s="3" t="s">
+      <c r="I92" s="2" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="3" t="s">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G93" s="3" t="s">
+      <c r="G93" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="I93" s="3" t="s">
+      <c r="I93" s="2" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="s">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C94" s="3" t="s">
+      <c r="C94" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="I94" s="3" t="s">
+      <c r="I94" s="2" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="C95" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="I95" s="3" t="s">
+      <c r="I95" s="2" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C96" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G96" s="3" t="s">
+      <c r="G96" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="I96" s="3" t="s">
+      <c r="I96" s="2" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C97" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G97" s="3" t="s">
+      <c r="G97" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="I97" s="3" t="s">
+      <c r="I97" s="2" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C98" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G98" s="3" t="s">
+      <c r="G98" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="I98" s="3" t="s">
+      <c r="I98" s="2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="I99" s="3" t="s">
+      <c r="I99" s="2" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="C100" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G100" s="3" t="s">
+      <c r="G100" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="I100" s="3" t="s">
+      <c r="I100" s="2" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I101" s="3" t="s">
+      <c r="I101" s="2" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C102" s="3" t="s">
+      <c r="C102" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G102" s="3" t="s">
+      <c r="G102" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="I102" s="3" t="s">
+      <c r="I102" s="2" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="3" t="s">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C103" s="3" t="s">
+      <c r="C103" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G103" s="3" t="s">
+      <c r="G103" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="I103" s="3" t="s">
+      <c r="I103" s="2" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="3" t="s">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C104" s="3" t="s">
+      <c r="C104" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G104" s="3" t="s">
+      <c r="G104" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="I104" s="3" t="s">
+      <c r="I104" s="2" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="3" t="s">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C105" s="3" t="s">
+      <c r="C105" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G105" s="3" t="s">
+      <c r="G105" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="I105" s="3" t="s">
+      <c r="I105" s="2" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="3" t="s">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C106" s="3" t="s">
+      <c r="C106" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="G106" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="I106" s="3" t="s">
+      <c r="I106" s="2" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="3" t="s">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C107" s="3" t="s">
+      <c r="C107" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G107" s="3" t="s">
+      <c r="G107" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="I107" s="3" t="s">
+      <c r="I107" s="2" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="3" t="s">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C108" s="3" t="s">
+      <c r="C108" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G108" s="3" t="s">
+      <c r="G108" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="I108" s="3" t="s">
+      <c r="I108" s="2" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="3" t="s">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C109" s="3" t="s">
+      <c r="C109" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G109" s="3" t="s">
+      <c r="G109" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="I109" s="3" t="s">
+      <c r="I109" s="2" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="3" t="s">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C110" s="3" t="s">
+      <c r="C110" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G110" s="3" t="s">
+      <c r="G110" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="I110" s="3" t="s">
+      <c r="I110" s="2" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="3" t="s">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="C111" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G111" s="3" t="s">
+      <c r="G111" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="I111" s="3" t="s">
+      <c r="I111" s="2" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="3" t="s">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C112" s="3" t="s">
+      <c r="C112" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G112" s="3" t="s">
+      <c r="G112" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="I112" s="3" t="s">
+      <c r="I112" s="2" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="3" t="s">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="C113" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D113" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G113" s="3" t="s">
+      <c r="G113" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I113" s="3" t="s">
+      <c r="I113" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="L113" s="3" t="s">
+      <c r="L113" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="M113" s="3" t="s">
+      <c r="M113" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="3" t="s">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C114" s="3" t="s">
+      <c r="C114" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D114" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="G114" s="3" t="s">
+      <c r="G114" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="I114" s="3" t="s">
+      <c r="I114" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="L114" s="3" t="s">
+      <c r="L114" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="M114" s="3" t="s">
+      <c r="M114" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="3" t="s">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C115" s="3" t="s">
+      <c r="C115" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D115" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="I115" s="3" t="s">
+      <c r="I115" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="L115" s="3" t="s">
+      <c r="L115" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="M115" s="3" t="s">
+      <c r="M115" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="3" t="s">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C116" s="3" t="s">
+      <c r="C116" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D116" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="I116" s="3" t="s">
+      <c r="I116" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="L116" s="3" t="s">
+      <c r="L116" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="M116" s="3" t="s">
+      <c r="M116" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="3" t="s">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C117" s="3" t="s">
+      <c r="C117" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D117" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="I117" s="3" t="s">
+      <c r="I117" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="L117" s="3" t="s">
+      <c r="L117" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="M117" s="3" t="s">
+      <c r="M117" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="3" t="s">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C118" s="3" t="s">
+      <c r="C118" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D118" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G118" s="3" t="s">
+      <c r="G118" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="I118" s="3" t="s">
+      <c r="I118" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="L118" s="3" t="s">
+      <c r="L118" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="M118" s="3" t="s">
+      <c r="M118" s="2" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="3" t="s">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C119" s="3" t="s">
+      <c r="C119" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="I119" s="3" t="s">
+      <c r="I119" s="2" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="3" t="s">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G120" s="3" t="s">
+      <c r="G120" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="I120" s="3" t="s">
+      <c r="I120" s="2" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="3" t="s">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C121" s="3" t="s">
+      <c r="C121" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G121" s="3" t="s">
+      <c r="G121" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="I121" s="3" t="s">
+      <c r="I121" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="s">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C122" s="3" t="s">
+      <c r="C122" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G122" s="3" t="s">
+      <c r="G122" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="I122" s="3" t="s">
+      <c r="I122" s="2" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="s">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G123" s="3" t="s">
+      <c r="G123" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="I123" s="3" t="s">
+      <c r="I123" s="2" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="3" t="s">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C124" s="3" t="s">
+      <c r="C124" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G124" s="3" t="s">
+      <c r="G124" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="I124" s="3" t="s">
+      <c r="I124" s="2" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="3" t="s">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C125" s="3" t="s">
+      <c r="C125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D125" s="3" t="s">
+      <c r="D125" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G125" s="3" t="s">
+      <c r="G125" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="I125" s="3" t="s">
+      <c r="I125" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="L125" s="3" t="s">
+      <c r="L125" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="M125" s="3" t="s">
+      <c r="M125" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="3" t="s">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C126" s="3" t="s">
+      <c r="C126" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D126" s="3" t="s">
+      <c r="D126" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="G126" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="I126" s="3" t="s">
+      <c r="I126" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="L126" s="3" t="s">
+      <c r="L126" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="M126" s="3" t="s">
+      <c r="M126" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="s">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C127" s="3" t="s">
+      <c r="C127" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D127" s="3" t="s">
+      <c r="D127" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G127" s="3" t="s">
+      <c r="G127" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="I127" s="3" t="s">
+      <c r="I127" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="L127" s="3" t="s">
+      <c r="L127" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="M127" s="3" t="s">
+      <c r="M127" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="3" t="s">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C128" s="3" t="s">
+      <c r="C128" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D128" s="3" t="s">
+      <c r="D128" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G128" s="3" t="s">
+      <c r="G128" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="I128" s="3" t="s">
+      <c r="I128" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="L128" s="3" t="s">
+      <c r="L128" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="M128" s="3" t="s">
+      <c r="M128" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="3" t="s">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C129" s="3" t="s">
+      <c r="C129" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G129" s="3" t="s">
+      <c r="G129" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="I129" s="3" t="s">
+      <c r="I129" s="2" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="3" t="s">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C130" s="3" t="s">
+      <c r="C130" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D130" s="3" t="s">
+      <c r="D130" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G130" s="3" t="s">
+      <c r="G130" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="I130" s="3" t="s">
+      <c r="I130" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="L130" s="3" t="s">
+      <c r="L130" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="M130" s="3" t="s">
+      <c r="M130" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="3" t="s">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C131" s="3" t="s">
+      <c r="C131" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D131" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G131" s="3" t="s">
+      <c r="G131" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="I131" s="3" t="s">
+      <c r="I131" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="L131" s="3" t="s">
+      <c r="L131" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="M131" s="3" t="s">
+      <c r="M131" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="3" t="s">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C132" s="3" t="s">
+      <c r="C132" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D132" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="G132" s="3" t="s">
+      <c r="G132" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="I132" s="3" t="s">
+      <c r="I132" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="L132" s="3" t="s">
+      <c r="L132" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="M132" s="3" t="s">
+      <c r="M132" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="3" t="s">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C133" s="3" t="s">
+      <c r="C133" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D133" s="3" t="s">
+      <c r="D133" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G133" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="I133" s="3" t="s">
+      <c r="I133" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="L133" s="3" t="s">
+      <c r="L133" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="M133" s="3" t="s">
+      <c r="M133" s="2" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="3" t="s">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C134" s="3" t="s">
+      <c r="C134" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G134" s="3" t="s">
+      <c r="G134" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="I134" s="3" t="s">
+      <c r="I134" s="2" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="3" t="s">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C135" s="3" t="s">
+      <c r="C135" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="I135" s="3" t="s">
+      <c r="I135" s="2" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="3" t="s">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C136" s="3" t="s">
+      <c r="C136" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G136" s="3" t="s">
+      <c r="G136" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="I136" s="3" t="s">
+      <c r="I136" s="2" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="3" t="s">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C137" s="3" t="s">
+      <c r="C137" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G137" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="I137" s="3" t="s">
+      <c r="I137" s="2" t="s">
         <v>471</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="3" t="s">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D138" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G138" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="I138" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="L138" s="3" t="s">
+      <c r="L138" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="M138" s="3" t="s">
+      <c r="M138" s="2" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="3" t="s">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C139" s="3" t="s">
+      <c r="C139" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D139" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G139" s="3" t="s">
+      <c r="G139" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="I139" s="3" t="s">
+      <c r="I139" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="L139" s="3" t="s">
+      <c r="L139" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="M139" s="3" t="s">
+      <c r="M139" s="2" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="3" t="s">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C140" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G140" s="3" t="s">
+      <c r="G140" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="I140" s="3" t="s">
+      <c r="I140" s="2" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="3" t="s">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G141" s="3" t="s">
+      <c r="G141" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="I141" s="3" t="s">
+      <c r="I141" s="2" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="3" t="s">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C142" s="3" t="s">
+      <c r="C142" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="I142" s="3" t="s">
+      <c r="I142" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="L142" s="3" t="s">
+      <c r="L142" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M142" s="3" t="s">
+      <c r="M142" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="3" t="s">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C143" s="3" t="s">
+      <c r="C143" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D143" s="3" t="s">
+      <c r="D143" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="G143" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="I143" s="3" t="s">
+      <c r="I143" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="L143" s="3" t="s">
+      <c r="L143" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M143" s="3" t="s">
+      <c r="M143" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="3" t="s">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C144" s="3" t="s">
+      <c r="C144" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D144" s="3" t="s">
+      <c r="D144" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="I144" s="3" t="s">
+      <c r="I144" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="L144" s="3" t="s">
+      <c r="L144" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M144" s="3" t="s">
+      <c r="M144" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="3" t="s">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C145" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="D145" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G145" s="3" t="s">
+      <c r="G145" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="I145" s="3" t="s">
+      <c r="I145" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="L145" s="3" t="s">
+      <c r="L145" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M145" s="3" t="s">
+      <c r="M145" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="3" t="s">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C146" s="3" t="s">
+      <c r="C146" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="D146" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G146" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="I146" s="3" t="s">
+      <c r="I146" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="L146" s="3" t="s">
+      <c r="L146" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M146" s="3" t="s">
+      <c r="M146" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="3" t="s">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="B147" s="3" t="s">
+      <c r="B147" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C147" s="3" t="s">
+      <c r="C147" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="G147" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="I147" s="3" t="s">
+      <c r="I147" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="L147" s="3" t="s">
+      <c r="L147" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M147" s="3" t="s">
+      <c r="M147" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="3" t="s">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B148" s="3" t="s">
+      <c r="B148" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C148" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D148" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G148" s="3" t="s">
+      <c r="G148" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="I148" s="3" t="s">
+      <c r="I148" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="L148" s="3" t="s">
+      <c r="L148" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="M148" s="3" t="s">
+      <c r="M148" s="2" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="3" t="s">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B149" s="3" t="s">
+      <c r="B149" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C149" s="3" t="s">
+      <c r="C149" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G149" s="3" t="s">
+      <c r="G149" s="2" t="s">
         <v>511</v>
       </c>
-      <c r="I149" s="3" t="s">
+      <c r="I149" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="L149" s="3" t="s">
+      <c r="L149" s="2" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="3" t="s">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B150" s="3" t="s">
+      <c r="B150" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C150" s="3" t="s">
+      <c r="C150" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D150" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G150" s="3" t="s">
+      <c r="G150" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="I150" s="3" t="s">
+      <c r="I150" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="L150" s="3" t="s">
+      <c r="L150" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="M150" s="3" t="s">
+      <c r="M150" s="2" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="3" t="s">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B151" s="3" t="s">
+      <c r="B151" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C151" s="3" t="s">
+      <c r="C151" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G151" s="3" t="s">
+      <c r="G151" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="I151" s="3" t="s">
+      <c r="I151" s="2" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="3" t="s">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B152" s="3" t="s">
+      <c r="B152" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C152" s="3" t="s">
+      <c r="C152" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="D152" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G152" s="3" t="s">
+      <c r="G152" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="I152" s="3" t="s">
+      <c r="I152" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="L152" s="3" t="s">
+      <c r="L152" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="M152" s="3" t="s">
+      <c r="M152" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="3" t="s">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B153" s="3" t="s">
+      <c r="B153" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C153" s="3" t="s">
+      <c r="C153" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G153" s="3" t="s">
+      <c r="G153" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="I153" s="3" t="s">
+      <c r="I153" s="2" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="3" t="s">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B154" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="G154" s="3" t="s">
+      <c r="G154" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="I154" s="3" t="s">
+      <c r="I154" s="2" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="3" t="s">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B155" s="3" t="s">
+      <c r="B155" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C155" s="3" t="s">
+      <c r="C155" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G155" s="3" t="s">
+      <c r="G155" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="I155" s="3" t="s">
+      <c r="I155" s="2" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="3" t="s">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B156" s="3" t="s">
+      <c r="B156" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C156" s="3" t="s">
+      <c r="C156" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D156" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="G156" s="3" t="s">
+      <c r="G156" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="I156" s="3" t="s">
+      <c r="I156" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="L156" s="3" t="s">
+      <c r="L156" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="M156" s="3" t="s">
+      <c r="M156" s="2" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="3" t="s">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B157" s="3" t="s">
+      <c r="B157" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C157" s="3" t="s">
+      <c r="C157" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D157" s="3" t="s">
+      <c r="D157" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G157" s="3" t="s">
+      <c r="G157" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="I157" s="3" t="s">
+      <c r="I157" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="L157" s="3" t="s">
+      <c r="L157" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="M157" s="3" t="s">
+      <c r="M157" s="2" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="3" t="s">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="B158" s="3" t="s">
+      <c r="B158" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C158" s="3" t="s">
+      <c r="C158" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D158" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G158" s="3" t="s">
+      <c r="G158" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="I158" s="3" t="s">
+      <c r="I158" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="L158" s="3" t="s">
+      <c r="L158" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="M158" s="3" t="s">
+      <c r="M158" s="2" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="3" t="s">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="B159" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C159" s="3" t="s">
+      <c r="C159" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D159" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G159" s="3" t="s">
+      <c r="G159" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="I159" s="3" t="s">
+      <c r="I159" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="L159" s="3" t="s">
+      <c r="L159" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="M159" s="3" t="s">
+      <c r="M159" s="2" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="3" t="s">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="B160" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C160" s="3" t="s">
+      <c r="C160" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D160" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="I160" s="3" t="s">
+      <c r="I160" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="L160" s="3" t="s">
+      <c r="L160" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="M160" s="3" t="s">
+      <c r="M160" s="2" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="3" t="s">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="B161" s="3" t="s">
+      <c r="B161" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C161" s="3" t="s">
+      <c r="C161" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G161" s="3" t="s">
+      <c r="G161" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="I161" s="3" t="s">
+      <c r="I161" s="2" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="3" t="s">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B162" s="3" t="s">
+      <c r="B162" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C162" s="3" t="s">
+      <c r="C162" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D162" s="3" t="s">
+      <c r="D162" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="G162" s="3" t="s">
+      <c r="G162" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="I162" s="3" t="s">
+      <c r="I162" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="L162" s="3" t="s">
+      <c r="L162" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="M162" s="3" t="s">
+      <c r="M162" s="2" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="3" t="s">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B163" s="3" t="s">
+      <c r="B163" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C163" s="3" t="s">
+      <c r="C163" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D163" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G163" s="3" t="s">
+      <c r="G163" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="I163" s="3" t="s">
+      <c r="I163" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="L163" s="3" t="s">
+      <c r="L163" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="M163" s="3" t="s">
+      <c r="M163" s="2" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="3" t="s">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B164" s="3" t="s">
+      <c r="B164" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="C164" s="3" t="s">
+      <c r="C164" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D164" s="3" t="s">
+      <c r="D164" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G164" s="3" t="s">
+      <c r="G164" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="I164" s="3" t="s">
+      <c r="I164" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="L164" s="3" t="s">
+      <c r="L164" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="M164" s="3" t="s">
+      <c r="M164" s="2" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="3" t="s">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="B165" s="3" t="s">
+      <c r="B165" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G165" s="3" t="s">
+      <c r="G165" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="I165" s="3" t="s">
+      <c r="I165" s="2" t="s">
         <v>565</v>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="3" t="s">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="B166" s="3" t="s">
+      <c r="B166" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C166" s="3" t="s">
+      <c r="C166" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G166" s="3" t="s">
+      <c r="G166" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="I166" s="3" t="s">
+      <c r="I166" s="2" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="3" t="s">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="B167" s="3" t="s">
+      <c r="B167" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C167" s="3" t="s">
+      <c r="C167" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D167" s="3" t="s">
+      <c r="D167" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G167" s="3" t="s">
+      <c r="G167" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="I167" s="3" t="s">
+      <c r="I167" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="L167" s="3" t="s">
+      <c r="L167" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="M167" s="3" t="s">
+      <c r="M167" s="2" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="3" t="s">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B168" s="3" t="s">
+      <c r="B168" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C168" s="3" t="s">
+      <c r="C168" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D168" s="3" t="s">
+      <c r="D168" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G168" s="3" t="s">
+      <c r="G168" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="I168" s="3" t="s">
+      <c r="I168" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="L168" s="3" t="s">
+      <c r="L168" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="M168" s="3" t="s">
+      <c r="M168" s="2" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="3" t="s">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="B169" s="3" t="s">
+      <c r="B169" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C169" s="3" t="s">
+      <c r="C169" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G169" s="3" t="s">
+      <c r="G169" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="I169" s="3" t="s">
+      <c r="I169" s="2" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="3" t="s">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="B170" s="3" t="s">
+      <c r="B170" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C170" s="3" t="s">
+      <c r="C170" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D170" s="3" t="s">
+      <c r="D170" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G170" s="3" t="s">
+      <c r="G170" s="2" t="s">
         <v>580</v>
       </c>
-      <c r="I170" s="3" t="s">
+      <c r="I170" s="2" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="3" t="s">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="B171" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C171" s="3" t="s">
+      <c r="C171" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D171" s="3" t="s">
+      <c r="D171" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="G171" s="3" t="s">
+      <c r="G171" s="2" t="s">
         <v>583</v>
       </c>
-      <c r="I171" s="3" t="s">
+      <c r="I171" s="2" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="3" t="s">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="B172" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C172" s="3" t="s">
+      <c r="C172" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D172" s="3" t="s">
+      <c r="D172" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="G172" s="3" t="s">
+      <c r="G172" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="I172" s="3" t="s">
+      <c r="I172" s="2" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="3" t="s">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B173" s="3" t="s">
+      <c r="B173" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C173" s="3" t="s">
+      <c r="C173" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D173" s="3" t="s">
+      <c r="D173" s="2" t="s">
         <v>590</v>
       </c>
-      <c r="G173" s="3" t="s">
+      <c r="G173" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="I173" s="3" t="s">
+      <c r="I173" s="2" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="3" t="s">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B174" s="3" t="s">
+      <c r="B174" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C174" s="3" t="s">
+      <c r="C174" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D174" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G174" s="3" t="s">
+      <c r="G174" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="I174" s="3" t="s">
+      <c r="I174" s="2" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="3" t="s">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="B175" s="3" t="s">
+      <c r="B175" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C175" s="3" t="s">
+      <c r="C175" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D175" s="3" t="s">
+      <c r="D175" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G175" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="I175" s="3" t="s">
+      <c r="I175" s="2" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="3" t="s">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B176" s="3" t="s">
+      <c r="B176" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C176" s="3" t="s">
+      <c r="C176" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G176" s="3" t="s">
+      <c r="G176" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="I176" s="3" t="s">
+      <c r="I176" s="2" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="3" t="s">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B177" s="3" t="s">
+      <c r="B177" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C177" s="3" t="s">
+      <c r="C177" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D177" s="3" t="s">
+      <c r="D177" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G177" s="3" t="s">
+      <c r="G177" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="I177" s="3" t="s">
+      <c r="I177" s="2" t="s">
         <v>605</v>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="3" t="s">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B178" s="3" t="s">
+      <c r="B178" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C178" s="3" t="s">
+      <c r="C178" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D178" s="3" t="s">
+      <c r="D178" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G178" s="3" t="s">
+      <c r="G178" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="I178" s="3" t="s">
+      <c r="I178" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="L178" s="3" t="s">
+      <c r="L178" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="M178" s="3" t="s">
+      <c r="M178" s="2" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="3" t="s">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="B179" s="3" t="s">
+      <c r="B179" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C179" s="3" t="s">
+      <c r="C179" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D179" s="3" t="s">
+      <c r="D179" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G179" s="3" t="s">
+      <c r="G179" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="I179" s="3" t="s">
+      <c r="I179" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="L179" s="3" t="s">
+      <c r="L179" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="M179" s="3" t="s">
+      <c r="M179" s="2" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="3" t="s">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B180" s="3" t="s">
+      <c r="B180" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C180" s="3" t="s">
+      <c r="C180" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D180" s="3" t="s">
+      <c r="D180" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="I180" s="3" t="s">
+      <c r="I180" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="L180" s="3" t="s">
+      <c r="L180" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="M180" s="3" t="s">
+      <c r="M180" s="2" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="3" t="s">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B181" s="3" t="s">
+      <c r="B181" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C181" s="3" t="s">
+      <c r="C181" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D181" s="3" t="s">
+      <c r="D181" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="I181" s="3" t="s">
+      <c r="I181" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="L181" s="3" t="s">
+      <c r="L181" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="M181" s="3" t="s">
+      <c r="M181" s="2" t="s">
         <v>619</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="3" t="s">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="B182" s="3" t="s">
+      <c r="B182" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C182" s="3" t="s">
+      <c r="C182" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D182" s="3" t="s">
+      <c r="D182" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G182" s="3" t="s">
+      <c r="G182" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="I182" s="3" t="s">
+      <c r="I182" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="L182" s="3" t="s">
+      <c r="L182" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="M182" s="3" t="s">
+      <c r="M182" s="2" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="3" t="s">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="B183" s="3" t="s">
+      <c r="B183" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C183" s="3" t="s">
+      <c r="C183" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D183" s="3" t="s">
+      <c r="D183" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G183" s="3" t="s">
+      <c r="G183" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="I183" s="3" t="s">
+      <c r="I183" s="2" t="s">
         <v>625</v>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="3" t="s">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B184" s="3" t="s">
+      <c r="B184" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C184" s="3" t="s">
+      <c r="C184" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G184" s="3" t="s">
+      <c r="G184" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="I184" s="3" t="s">
+      <c r="I184" s="2" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="3" t="s">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="B185" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C185" s="3" t="s">
+      <c r="C185" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D185" s="3" t="s">
+      <c r="D185" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G185" s="3" t="s">
+      <c r="G185" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="I185" s="3" t="s">
+      <c r="I185" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="L185" s="3" t="s">
+      <c r="L185" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="M185" s="3" t="s">
+      <c r="M185" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="3" t="s">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="B186" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C186" s="3" t="s">
+      <c r="C186" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D186" s="3" t="s">
+      <c r="D186" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G186" s="3" t="s">
+      <c r="G186" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="I186" s="3" t="s">
+      <c r="I186" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="L186" s="3" t="s">
+      <c r="L186" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="M186" s="3" t="s">
+      <c r="M186" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="3" t="s">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="B187" s="3" t="s">
+      <c r="B187" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="C187" s="3" t="s">
+      <c r="C187" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D187" s="3" t="s">
+      <c r="D187" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G187" s="3" t="s">
+      <c r="G187" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="I187" s="3" t="s">
+      <c r="I187" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="L187" s="3" t="s">
+      <c r="L187" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="M187" s="3" t="s">
+      <c r="M187" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="3" t="s">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="B188" s="3" t="s">
+      <c r="B188" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G188" s="3" t="s">
+      <c r="G188" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="I188" s="3" t="s">
+      <c r="I188" s="2" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="189">
-      <c r="A189" s="3" t="s">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B189" s="3" t="s">
+      <c r="B189" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C189" s="3" t="s">
+      <c r="C189" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G189" s="3" t="s">
+      <c r="G189" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="I189" s="3" t="s">
+      <c r="I189" s="2" t="s">
         <v>644</v>
       </c>
     </row>
-    <row r="190">
-      <c r="A190" s="3" t="s">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="B190" s="3" t="s">
+      <c r="B190" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C190" s="3" t="s">
+      <c r="C190" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D190" s="3" t="s">
+      <c r="D190" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="G190" s="3" t="s">
+      <c r="G190" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="I190" s="3" t="s">
+      <c r="I190" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="L190" s="3" t="s">
+      <c r="L190" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="M190" s="3" t="s">
+      <c r="M190" s="2" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="3" t="s">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="B191" s="3" t="s">
+      <c r="B191" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C191" s="3" t="s">
+      <c r="C191" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D191" s="3" t="s">
+      <c r="D191" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="G191" s="2" t="s">
         <v>652</v>
       </c>
-      <c r="I191" s="3" t="s">
+      <c r="I191" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="L191" s="3" t="s">
+      <c r="L191" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="M191" s="3" t="s">
+      <c r="M191" s="2" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="3" t="s">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="B192" s="3" t="s">
+      <c r="B192" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C192" s="3" t="s">
+      <c r="C192" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D192" s="3" t="s">
+      <c r="D192" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G192" s="3" t="s">
+      <c r="G192" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="I192" s="3" t="s">
+      <c r="I192" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="L192" s="3" t="s">
+      <c r="L192" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="M192" s="3" t="s">
+      <c r="M192" s="2" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="3" t="s">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="B193" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C193" s="3" t="s">
+      <c r="C193" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D193" s="3" t="s">
+      <c r="D193" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="G193" s="3" t="s">
+      <c r="G193" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="I193" s="3" t="s">
+      <c r="I193" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="L193" s="3" t="s">
+      <c r="L193" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="M193" s="3" t="s">
+      <c r="M193" s="2" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="3" t="s">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B194" s="3" t="s">
+      <c r="B194" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C194" s="3" t="s">
+      <c r="C194" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G194" s="3" t="s">
+      <c r="G194" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="I194" s="3" t="s">
+      <c r="I194" s="2" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="3" t="s">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B195" s="3" t="s">
+      <c r="B195" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C195" s="3" t="s">
+      <c r="C195" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D195" s="3" t="s">
+      <c r="D195" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G195" s="3" t="s">
+      <c r="G195" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="I195" s="3" t="s">
+      <c r="I195" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="L195" s="3" t="s">
+      <c r="L195" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="M195" s="3" t="s">
+      <c r="M195" s="2" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="3" t="s">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="B196" s="3" t="s">
+      <c r="B196" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C196" s="3" t="s">
+      <c r="C196" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D196" s="3" t="s">
+      <c r="D196" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G196" s="3" t="s">
+      <c r="G196" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="I196" s="3" t="s">
+      <c r="I196" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="L196" s="3" t="s">
+      <c r="L196" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="M196" s="3" t="s">
+      <c r="M196" s="2" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="3" t="s">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="B197" s="3" t="s">
+      <c r="B197" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C197" s="3" t="s">
+      <c r="C197" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D197" s="3" t="s">
+      <c r="D197" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G197" s="3" t="s">
+      <c r="G197" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="I197" s="3" t="s">
+      <c r="I197" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="L197" s="3" t="s">
+      <c r="L197" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="M197" s="3" t="s">
+      <c r="M197" s="2" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="198">
-      <c r="A198" s="3" t="s">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="B198" s="3" t="s">
+      <c r="B198" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C198" s="3" t="s">
+      <c r="C198" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D198" s="3" t="s">
+      <c r="D198" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G198" s="3" t="s">
+      <c r="G198" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="I198" s="3" t="s">
+      <c r="I198" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="L198" s="3" t="s">
+      <c r="L198" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="M198" s="3" t="s">
+      <c r="M198" s="2" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="199">
-      <c r="A199" s="3" t="s">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="B199" s="3" t="s">
+      <c r="B199" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C199" s="3" t="s">
+      <c r="C199" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D199" s="3" t="s">
+      <c r="D199" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G199" s="3" t="s">
+      <c r="G199" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="I199" s="3" t="s">
+      <c r="I199" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="L199" s="3" t="s">
+      <c r="L199" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="M199" s="3" t="s">
+      <c r="M199" s="2" t="s">
         <v>667</v>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="3" t="s">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="B200" s="3" t="s">
+      <c r="B200" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C200" s="3" t="s">
+      <c r="C200" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G200" s="3" t="s">
+      <c r="G200" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="I200" s="3" t="s">
+      <c r="I200" s="2" t="s">
         <v>682</v>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="s">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="B201" s="3" t="s">
+      <c r="B201" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C201" s="3" t="s">
+      <c r="C201" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D201" s="3" t="s">
+      <c r="D201" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="G201" s="3" t="s">
+      <c r="G201" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="I201" s="3" t="s">
+      <c r="I201" s="2" t="s">
         <v>686</v>
       </c>
-      <c r="L201" s="3" t="s">
+      <c r="L201" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="M201" s="3" t="s">
+      <c r="M201" s="2" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="3" t="s">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
         <v>688</v>
       </c>
-      <c r="B202" s="3" t="s">
+      <c r="B202" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C202" s="3" t="s">
+      <c r="C202" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D202" s="3" t="s">
+      <c r="D202" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="G202" s="3" t="s">
+      <c r="G202" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="I202" s="3" t="s">
+      <c r="I202" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="L202" s="3" t="s">
+      <c r="L202" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="M202" s="3" t="s">
+      <c r="M202" s="2" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="3" t="s">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="B203" s="3" t="s">
+      <c r="B203" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C203" s="3" t="s">
+      <c r="C203" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D203" s="3" t="s">
+      <c r="D203" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="G203" s="3" t="s">
+      <c r="G203" s="2" t="s">
         <v>694</v>
       </c>
-      <c r="I203" s="3" t="s">
+      <c r="I203" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="L203" s="3" t="s">
+      <c r="L203" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="M203" s="3" t="s">
+      <c r="M203" s="2" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="3" t="s">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="B204" s="3" t="s">
+      <c r="B204" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C204" s="3" t="s">
+      <c r="C204" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D204" s="3" t="s">
+      <c r="D204" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G204" s="3" t="s">
+      <c r="G204" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="I204" s="3" t="s">
+      <c r="I204" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="L204" s="3" t="s">
+      <c r="L204" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="M204" s="3" t="s">
+      <c r="M204" s="2" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="3" t="s">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="B205" s="3" t="s">
+      <c r="B205" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C205" s="3" t="s">
+      <c r="C205" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G205" s="3" t="s">
+      <c r="G205" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="I205" s="3" t="s">
+      <c r="I205" s="2" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="3" t="s">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="B206" s="3" t="s">
+      <c r="B206" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C206" s="3" t="s">
+      <c r="C206" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D206" s="3" t="s">
+      <c r="D206" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="G206" s="3" t="s">
+      <c r="G206" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="I206" s="3" t="s">
+      <c r="I206" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="L206" s="3" t="s">
+      <c r="L206" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="M206" s="3" t="s">
+      <c r="M206" s="2" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="3" t="s">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="B207" s="3" t="s">
+      <c r="B207" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C207" s="3" t="s">
+      <c r="C207" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D207" s="3" t="s">
+      <c r="D207" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G207" s="3" t="s">
+      <c r="G207" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="I207" s="3" t="s">
+      <c r="I207" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="L207" s="3" t="s">
+      <c r="L207" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="M207" s="3" t="s">
+      <c r="M207" s="2" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="3" t="s">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="B208" s="3" t="s">
+      <c r="B208" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C208" s="3" t="s">
+      <c r="C208" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D208" s="3" t="s">
+      <c r="D208" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G208" s="3" t="s">
+      <c r="G208" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="I208" s="3" t="s">
+      <c r="I208" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="L208" s="3" t="s">
+      <c r="L208" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="M208" s="3" t="s">
+      <c r="M208" s="2" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="3" t="s">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="B209" s="3" t="s">
+      <c r="B209" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C209" s="3" t="s">
+      <c r="C209" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D209" s="3" t="s">
+      <c r="D209" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G209" s="3" t="s">
+      <c r="G209" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="I209" s="3" t="s">
+      <c r="I209" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="L209" s="3" t="s">
+      <c r="L209" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="M209" s="3" t="s">
+      <c r="M209" s="2" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="210">
-      <c r="A210" s="3" t="s">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="B210" s="3" t="s">
+      <c r="B210" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C210" s="3" t="s">
+      <c r="C210" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="G210" s="3" t="s">
+      <c r="G210" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="I210" s="3" t="s">
+      <c r="I210" s="2" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="3" t="s">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B211" s="3" t="s">
+      <c r="B211" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C211" s="3" t="s">
+      <c r="C211" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G211" s="3" t="s">
+      <c r="G211" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="I211" s="3" t="s">
+      <c r="I211" s="2" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="3" t="s">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
         <v>721</v>
       </c>
-      <c r="B212" s="3" t="s">
+      <c r="B212" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C212" s="3" t="s">
+      <c r="C212" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="D212" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="G212" s="3" t="s">
+      <c r="G212" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="I212" s="3" t="s">
+      <c r="I212" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="L212" s="3" t="s">
+      <c r="L212" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="M212" s="3" t="s">
+      <c r="M212" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="3" t="s">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B213" s="3" t="s">
+      <c r="B213" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C213" s="3" t="s">
+      <c r="C213" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D213" s="3" t="s">
+      <c r="D213" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="G213" s="3" t="s">
+      <c r="G213" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="I213" s="3" t="s">
+      <c r="I213" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="L213" s="3" t="s">
+      <c r="L213" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="M213" s="3" t="s">
+      <c r="M213" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="214">
-      <c r="A214" s="3" t="s">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
         <v>729</v>
       </c>
-      <c r="B214" s="3" t="s">
+      <c r="B214" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C214" s="3" t="s">
+      <c r="C214" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D214" s="3" t="s">
+      <c r="D214" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="G214" s="3" t="s">
+      <c r="G214" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="I214" s="3" t="s">
+      <c r="I214" s="2" t="s">
         <v>732</v>
       </c>
-      <c r="L214" s="3" t="s">
+      <c r="L214" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="M214" s="3" t="s">
+      <c r="M214" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="3" t="s">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B215" s="3" t="s">
+      <c r="B215" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C215" s="3" t="s">
+      <c r="C215" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D215" s="3" t="s">
+      <c r="D215" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="G215" s="3" t="s">
+      <c r="G215" s="2" t="s">
         <v>734</v>
       </c>
-      <c r="I215" s="3" t="s">
+      <c r="I215" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="L215" s="3" t="s">
+      <c r="L215" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="M215" s="3" t="s">
+      <c r="M215" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="216">
-      <c r="A216" s="3" t="s">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="B216" s="3" t="s">
+      <c r="B216" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C216" s="3" t="s">
+      <c r="C216" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D216" s="3" t="s">
+      <c r="D216" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="G216" s="3" t="s">
+      <c r="G216" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="I216" s="3" t="s">
+      <c r="I216" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="L216" s="3" t="s">
+      <c r="L216" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="M216" s="3" t="s">
+      <c r="M216" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217" s="3" t="s">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B217" s="3" t="s">
+      <c r="B217" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C217" s="3" t="s">
+      <c r="C217" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G217" s="3" t="s">
+      <c r="G217" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="I217" s="3" t="s">
+      <c r="I217" s="2" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="218">
-      <c r="A218" s="3" t="s">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="B218" s="3" t="s">
+      <c r="B218" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G218" s="3" t="s">
+      <c r="G218" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="I218" s="3" t="s">
+      <c r="I218" s="2" t="s">
         <v>744</v>
       </c>
     </row>
-    <row r="219">
-      <c r="A219" s="3" t="s">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="B219" s="3" t="s">
+      <c r="B219" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C219" s="3" t="s">
+      <c r="C219" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G219" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="I219" s="3" t="s">
+      <c r="I219" s="2" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="3" t="s">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="B220" s="3" t="s">
+      <c r="B220" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C220" s="3" t="s">
+      <c r="C220" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="G220" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="I220" s="3" t="s">
+      <c r="I220" s="2" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="3" t="s">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B221" s="3" t="s">
+      <c r="B221" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C221" s="3" t="s">
+      <c r="C221" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G221" s="3" t="s">
+      <c r="G221" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="I221" s="3" t="s">
+      <c r="I221" s="2" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="3" t="s">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="B222" s="3" t="s">
+      <c r="B222" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C222" s="3" t="s">
+      <c r="C222" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G222" s="3" t="s">
+      <c r="G222" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="I222" s="3" t="s">
+      <c r="I222" s="2" t="s">
         <v>756</v>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" s="3" t="s">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="B223" s="3" t="s">
+      <c r="B223" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C223" s="3" t="s">
+      <c r="C223" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D223" s="3" t="s">
+      <c r="D223" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G223" s="3" t="s">
+      <c r="G223" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="I223" s="3" t="s">
+      <c r="I223" s="2" t="s">
         <v>759</v>
       </c>
     </row>
-    <row r="224">
-      <c r="A224" s="3" t="s">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="B224" s="3" t="s">
+      <c r="B224" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C224" s="3" t="s">
+      <c r="C224" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D224" s="3" t="s">
+      <c r="D224" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="G224" s="3" t="s">
+      <c r="G224" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="I224" s="3" t="s">
+      <c r="I224" s="2" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="3" t="s">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
         <v>763</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="B225" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="C225" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D225" s="3" t="s">
+      <c r="D225" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G225" s="3" t="s">
+      <c r="G225" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="I225" s="3" t="s">
+      <c r="I225" s="2" t="s">
         <v>765</v>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="3" t="s">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="B226" s="3" t="s">
+      <c r="B226" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C226" s="3" t="s">
+      <c r="C226" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G226" s="3" t="s">
+      <c r="G226" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="I226" s="3" t="s">
+      <c r="I226" s="2" t="s">
         <v>768</v>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="3" t="s">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="B227" s="3" t="s">
+      <c r="B227" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G227" s="3" t="s">
+      <c r="G227" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="I227" s="3" t="s">
+      <c r="I227" s="2" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="3" t="s">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
         <v>772</v>
       </c>
-      <c r="B228" s="3" t="s">
+      <c r="B228" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C228" s="3" t="s">
+      <c r="C228" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="G228" s="3" t="s">
+      <c r="G228" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="I228" s="3" t="s">
+      <c r="I228" s="2" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="3" t="s">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="B229" s="3" t="s">
+      <c r="B229" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="G229" s="3" t="s">
+      <c r="G229" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="I229" s="3" t="s">
+      <c r="I229" s="2" t="s">
         <v>777</v>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="3" t="s">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="B230" s="3" t="s">
+      <c r="B230" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C230" s="3" t="s">
+      <c r="C230" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G230" s="3" t="s">
+      <c r="G230" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="I230" s="3" t="s">
+      <c r="I230" s="2" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="3" t="s">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
         <v>781</v>
       </c>
-      <c r="B231" s="3" t="s">
+      <c r="B231" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C231" s="3" t="s">
+      <c r="C231" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G231" s="3" t="s">
+      <c r="G231" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="I231" s="3" t="s">
+      <c r="I231" s="2" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="3" t="s">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="B232" s="3" t="s">
+      <c r="B232" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C232" s="3" t="s">
+      <c r="C232" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G232" s="3" t="s">
+      <c r="G232" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="I232" s="3" t="s">
+      <c r="I232" s="2" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="3" t="s">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="B233" s="3" t="s">
+      <c r="B233" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C233" s="3" t="s">
+      <c r="C233" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="G233" s="3" t="s">
+      <c r="G233" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I233" s="3" t="s">
+      <c r="I233" s="2" t="s">
         <v>789</v>
       </c>
     </row>
@@ -8019,9 +8025,8 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>